--- a/data27crit.xlsx
+++ b/data27crit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vincent MOUSSEAU\Dropbox\- Centrale\Pédagogie\Decision Making-ORRA\2025-26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Bureau\CS\partie2\SDP\SDP_gurobi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD2E528-97B4-4F8D-9779-69FFE634A409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAA0034-08AA-4613-A060-1975E5F264B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{ED726CF5-01AA-4825-830A-635C7D11D368}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ED726CF5-01AA-4825-830A-635C7D11D368}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
-  <si>
-    <t>weight</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>solution 1</t>
   </si>
@@ -134,16 +131,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>decision involving 27 criteria named a,b,c,…,y,z,A</t>
-  </si>
-  <si>
-    <t>the weight vector is provided on row 6</t>
-  </si>
-  <si>
-    <t>Explain that solution 1 is better than all other three solutions</t>
-  </si>
-  <si>
-    <t>$</t>
+    <t>weights</t>
   </si>
 </sst>
 </file>
@@ -515,115 +503,439 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BB9C46-63B9-41C3-8971-88854A3C7B1E}">
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>32</v>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>532</v>
+      </c>
+      <c r="C2">
+        <v>120</v>
+      </c>
+      <c r="D2">
+        <v>330</v>
+      </c>
+      <c r="E2">
+        <v>54</v>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>125</v>
+      </c>
+      <c r="H2">
+        <v>320</v>
+      </c>
+      <c r="I2">
+        <v>59.4</v>
+      </c>
+      <c r="J2">
+        <v>125</v>
+      </c>
+      <c r="K2">
+        <v>325</v>
+      </c>
+      <c r="L2">
+        <v>77</v>
+      </c>
+      <c r="M2">
+        <v>47.6</v>
+      </c>
+      <c r="N2">
+        <v>784</v>
+      </c>
+      <c r="O2">
+        <v>673</v>
+      </c>
+      <c r="P2">
+        <v>423</v>
+      </c>
+      <c r="Q2">
+        <v>221</v>
+      </c>
+      <c r="R2">
+        <v>164.6</v>
+      </c>
+      <c r="S2">
+        <v>125</v>
+      </c>
+      <c r="T2">
+        <v>577</v>
+      </c>
+      <c r="U2">
+        <v>231</v>
+      </c>
+      <c r="V2">
+        <v>677</v>
+      </c>
+      <c r="W2">
+        <v>32</v>
+      </c>
+      <c r="X2">
+        <v>197</v>
+      </c>
+      <c r="Y2">
+        <v>123</v>
+      </c>
+      <c r="Z2">
+        <v>224</v>
+      </c>
+      <c r="AA2">
+        <v>324.10000000000002</v>
+      </c>
+      <c r="AB2">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>94</v>
+      </c>
+      <c r="C3">
+        <v>-756</v>
+      </c>
+      <c r="D3">
+        <v>174.4</v>
+      </c>
+      <c r="E3">
+        <v>-254.66666666666669</v>
+      </c>
+      <c r="F3">
+        <v>225.5</v>
+      </c>
+      <c r="G3">
+        <v>162.33333333333334</v>
+      </c>
+      <c r="H3">
+        <v>670</v>
+      </c>
+      <c r="I3">
+        <v>19.971428571428568</v>
+      </c>
+      <c r="J3">
+        <v>127.5</v>
+      </c>
+      <c r="K3">
+        <v>37.666666666666686</v>
+      </c>
+      <c r="L3">
+        <v>139</v>
+      </c>
+      <c r="M3">
+        <v>61.2</v>
+      </c>
+      <c r="N3">
+        <v>260</v>
+      </c>
+      <c r="O3">
+        <v>189</v>
+      </c>
+      <c r="P3">
+        <v>43</v>
+      </c>
+      <c r="Q3">
+        <v>446</v>
+      </c>
+      <c r="R3">
+        <v>267.39999999999998</v>
+      </c>
+      <c r="S3">
+        <v>239.33333333333331</v>
+      </c>
+      <c r="T3">
+        <v>155</v>
+      </c>
+      <c r="U3">
+        <v>349</v>
+      </c>
+      <c r="V3">
+        <v>363</v>
+      </c>
+      <c r="W3">
+        <v>206</v>
+      </c>
+      <c r="X3">
+        <v>294</v>
+      </c>
+      <c r="Y3">
+        <v>201</v>
+      </c>
+      <c r="Z3">
+        <v>214.8</v>
+      </c>
+      <c r="AA3">
+        <v>142.90000000000003</v>
+      </c>
+      <c r="AB3">
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>174</v>
+      </c>
+      <c r="C4">
+        <v>652</v>
+      </c>
+      <c r="D4">
+        <v>-1094</v>
+      </c>
+      <c r="E4">
+        <v>-176</v>
+      </c>
+      <c r="F4">
+        <v>-854</v>
+      </c>
+      <c r="G4">
+        <v>-573</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>50.6</v>
+      </c>
+      <c r="J4">
+        <v>515</v>
+      </c>
+      <c r="K4">
+        <v>-395</v>
+      </c>
+      <c r="L4">
+        <v>341</v>
+      </c>
+      <c r="M4">
+        <v>174.4</v>
+      </c>
+      <c r="N4">
+        <v>-1770</v>
+      </c>
+      <c r="O4">
+        <v>-581</v>
+      </c>
+      <c r="P4">
+        <v>-827</v>
+      </c>
+      <c r="Q4">
+        <v>605</v>
+      </c>
+      <c r="R4">
+        <v>-156.6</v>
+      </c>
+      <c r="S4">
+        <v>-479</v>
+      </c>
+      <c r="T4">
+        <v>107</v>
+      </c>
+      <c r="U4">
+        <v>-37</v>
+      </c>
+      <c r="V4">
+        <v>-483</v>
+      </c>
+      <c r="W4">
+        <v>706</v>
+      </c>
+      <c r="X4">
+        <v>-301</v>
+      </c>
+      <c r="Y4">
+        <v>27</v>
+      </c>
+      <c r="Z4">
+        <v>490</v>
+      </c>
+      <c r="AA4">
+        <v>-922.1</v>
+      </c>
+      <c r="AB4">
+        <v>-717</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>20</v>
-      </c>
-      <c r="R5" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" t="s">
-        <v>22</v>
-      </c>
-      <c r="T5" t="s">
-        <v>23</v>
-      </c>
-      <c r="U5" t="s">
-        <v>24</v>
-      </c>
-      <c r="V5" t="s">
-        <v>25</v>
-      </c>
-      <c r="W5" t="s">
-        <v>26</v>
-      </c>
-      <c r="X5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>31</v>
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>604</v>
+      </c>
+      <c r="C5">
+        <v>976</v>
+      </c>
+      <c r="D5">
+        <v>680</v>
+      </c>
+      <c r="E5">
+        <v>-52</v>
+      </c>
+      <c r="F5">
+        <v>-234</v>
+      </c>
+      <c r="G5">
+        <v>333</v>
+      </c>
+      <c r="H5">
+        <v>-254</v>
+      </c>
+      <c r="I5">
+        <v>-608.6</v>
+      </c>
+      <c r="J5">
+        <v>-523</v>
+      </c>
+      <c r="K5">
+        <v>277</v>
+      </c>
+      <c r="L5">
+        <v>-493</v>
+      </c>
+      <c r="M5">
+        <v>845.6</v>
+      </c>
+      <c r="N5">
+        <v>332</v>
+      </c>
+      <c r="O5">
+        <v>1351</v>
+      </c>
+      <c r="P5">
+        <v>1113</v>
+      </c>
+      <c r="Q5">
+        <v>675</v>
+      </c>
+      <c r="R5">
+        <v>294.60000000000002</v>
+      </c>
+      <c r="S5">
+        <v>927</v>
+      </c>
+      <c r="T5">
+        <v>-295</v>
+      </c>
+      <c r="U5">
+        <v>769</v>
+      </c>
+      <c r="V5">
+        <v>-39</v>
+      </c>
+      <c r="W5">
+        <v>-192</v>
+      </c>
+      <c r="X5">
+        <v>-509</v>
+      </c>
+      <c r="Y5">
+        <v>199</v>
+      </c>
+      <c r="Z5">
+        <v>54</v>
+      </c>
+      <c r="AA5">
+        <v>-393.9</v>
+      </c>
+      <c r="AB5">
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -705,350 +1017,6 @@
       </c>
       <c r="AB6">
         <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>532</v>
-      </c>
-      <c r="C8">
-        <v>120</v>
-      </c>
-      <c r="D8">
-        <v>330</v>
-      </c>
-      <c r="E8">
-        <v>54</v>
-      </c>
-      <c r="F8">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>125</v>
-      </c>
-      <c r="H8">
-        <v>320</v>
-      </c>
-      <c r="I8">
-        <v>59.4</v>
-      </c>
-      <c r="J8">
-        <v>125</v>
-      </c>
-      <c r="K8">
-        <v>325</v>
-      </c>
-      <c r="L8">
-        <v>77</v>
-      </c>
-      <c r="M8">
-        <v>47.6</v>
-      </c>
-      <c r="N8">
-        <v>784</v>
-      </c>
-      <c r="O8">
-        <v>673</v>
-      </c>
-      <c r="P8">
-        <v>423</v>
-      </c>
-      <c r="Q8">
-        <v>221</v>
-      </c>
-      <c r="R8">
-        <v>164.6</v>
-      </c>
-      <c r="S8">
-        <v>125</v>
-      </c>
-      <c r="T8">
-        <v>577</v>
-      </c>
-      <c r="U8">
-        <v>231</v>
-      </c>
-      <c r="V8">
-        <v>677</v>
-      </c>
-      <c r="W8">
-        <v>32</v>
-      </c>
-      <c r="X8">
-        <v>197</v>
-      </c>
-      <c r="Y8">
-        <v>123</v>
-      </c>
-      <c r="Z8">
-        <v>224</v>
-      </c>
-      <c r="AA8">
-        <v>324.10000000000002</v>
-      </c>
-      <c r="AB8">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>94</v>
-      </c>
-      <c r="C9">
-        <v>-756</v>
-      </c>
-      <c r="D9">
-        <v>174.4</v>
-      </c>
-      <c r="E9">
-        <v>-254.66666666666669</v>
-      </c>
-      <c r="F9">
-        <v>225.5</v>
-      </c>
-      <c r="G9">
-        <v>162.33333333333334</v>
-      </c>
-      <c r="H9">
-        <v>670</v>
-      </c>
-      <c r="I9">
-        <v>19.971428571428568</v>
-      </c>
-      <c r="J9">
-        <v>127.5</v>
-      </c>
-      <c r="K9">
-        <v>37.666666666666686</v>
-      </c>
-      <c r="L9">
-        <v>139</v>
-      </c>
-      <c r="M9">
-        <v>61.2</v>
-      </c>
-      <c r="N9">
-        <v>260</v>
-      </c>
-      <c r="O9">
-        <v>189</v>
-      </c>
-      <c r="P9">
-        <v>43</v>
-      </c>
-      <c r="Q9">
-        <v>446</v>
-      </c>
-      <c r="R9">
-        <v>267.39999999999998</v>
-      </c>
-      <c r="S9">
-        <v>239.33333333333331</v>
-      </c>
-      <c r="T9">
-        <v>155</v>
-      </c>
-      <c r="U9">
-        <v>349</v>
-      </c>
-      <c r="V9">
-        <v>363</v>
-      </c>
-      <c r="W9">
-        <v>206</v>
-      </c>
-      <c r="X9">
-        <v>294</v>
-      </c>
-      <c r="Y9">
-        <v>201</v>
-      </c>
-      <c r="Z9">
-        <v>214.8</v>
-      </c>
-      <c r="AA9">
-        <v>142.90000000000003</v>
-      </c>
-      <c r="AB9">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>174</v>
-      </c>
-      <c r="C10">
-        <v>652</v>
-      </c>
-      <c r="D10">
-        <v>-1094</v>
-      </c>
-      <c r="E10">
-        <v>-176</v>
-      </c>
-      <c r="F10">
-        <v>-854</v>
-      </c>
-      <c r="G10">
-        <v>-573</v>
-      </c>
-      <c r="H10">
-        <v>6</v>
-      </c>
-      <c r="I10">
-        <v>50.6</v>
-      </c>
-      <c r="J10">
-        <v>515</v>
-      </c>
-      <c r="K10">
-        <v>-395</v>
-      </c>
-      <c r="L10">
-        <v>341</v>
-      </c>
-      <c r="M10">
-        <v>174.4</v>
-      </c>
-      <c r="N10">
-        <v>-1770</v>
-      </c>
-      <c r="O10">
-        <v>-581</v>
-      </c>
-      <c r="P10">
-        <v>-827</v>
-      </c>
-      <c r="Q10">
-        <v>605</v>
-      </c>
-      <c r="R10">
-        <v>-156.6</v>
-      </c>
-      <c r="S10">
-        <v>-479</v>
-      </c>
-      <c r="T10">
-        <v>107</v>
-      </c>
-      <c r="U10">
-        <v>-37</v>
-      </c>
-      <c r="V10">
-        <v>-483</v>
-      </c>
-      <c r="W10">
-        <v>706</v>
-      </c>
-      <c r="X10">
-        <v>-301</v>
-      </c>
-      <c r="Y10">
-        <v>27</v>
-      </c>
-      <c r="Z10">
-        <v>490</v>
-      </c>
-      <c r="AA10">
-        <v>-922.1</v>
-      </c>
-      <c r="AB10">
-        <v>-717</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>604</v>
-      </c>
-      <c r="C11">
-        <v>976</v>
-      </c>
-      <c r="D11">
-        <v>680</v>
-      </c>
-      <c r="E11">
-        <v>-52</v>
-      </c>
-      <c r="F11">
-        <v>-234</v>
-      </c>
-      <c r="G11">
-        <v>333</v>
-      </c>
-      <c r="H11">
-        <v>-254</v>
-      </c>
-      <c r="I11">
-        <v>-608.6</v>
-      </c>
-      <c r="J11">
-        <v>-523</v>
-      </c>
-      <c r="K11">
-        <v>277</v>
-      </c>
-      <c r="L11">
-        <v>-493</v>
-      </c>
-      <c r="M11">
-        <v>845.6</v>
-      </c>
-      <c r="N11">
-        <v>332</v>
-      </c>
-      <c r="O11">
-        <v>1351</v>
-      </c>
-      <c r="P11">
-        <v>1113</v>
-      </c>
-      <c r="Q11">
-        <v>675</v>
-      </c>
-      <c r="R11">
-        <v>294.60000000000002</v>
-      </c>
-      <c r="S11">
-        <v>927</v>
-      </c>
-      <c r="T11">
-        <v>-295</v>
-      </c>
-      <c r="U11">
-        <v>769</v>
-      </c>
-      <c r="V11">
-        <v>-39</v>
-      </c>
-      <c r="W11">
-        <v>-192</v>
-      </c>
-      <c r="X11">
-        <v>-509</v>
-      </c>
-      <c r="Y11">
-        <v>199</v>
-      </c>
-      <c r="Z11">
-        <v>54</v>
-      </c>
-      <c r="AA11">
-        <v>-393.9</v>
-      </c>
-      <c r="AB11">
-        <v>617</v>
       </c>
     </row>
   </sheetData>
